--- a/hira_material_automation/output/monthly/202601_202609__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04T22:54:29</t>
+          <t>2026-09-14T23:45:59</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>92a0b4b7587cdcab1889db9aa858ae8875adf1f3b790fbe4b4ef4957cee5aba7</t>
+          <t>e1f27423fc9f33c04c754ba9aa79885e3813c5c6d7498d6789191e343651f1d4</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202609__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14T23:45:59</t>
+          <t>2026-09-24T23:49:25</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>e1f27423fc9f33c04c754ba9aa79885e3813c5c6d7498d6789191e343651f1d4</t>
+          <t>16a044dbbc4e12ef626f7c800f5f11c8cd86f0c96f0527fdce1ccc3ce2359236</t>
         </is>
       </c>
     </row>
